--- a/output/北塩原村_論点整理_20261009.xlsx
+++ b/output/北塩原村_論点整理_20261009.xlsx
@@ -827,7 +827,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>移植の申し送り（9件）と網羅性点検の残り12件を入れる先</t>
+          <t>移植の申し送り（20件）を令和8年10月10日に反映済み（北塩原村_計画素案_正本_移植後.docx）。網羅性点検の残り2件（Ｉ推計方法・Ｌ圏域の基盤整備）は回答待ち</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_論点整理_20261009.xlsx
+++ b/output/北塩原村_論点整理_20261009.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>村M-34〜M-39</t>
+          <t>村Ｍ-34〜Ｍ-39</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>論点メモが読んでいる版と正本が違う。正本の数値に読み替える。ただし正本の181人も他メンバーの策定ワークシートで「推計」と記された値であり、村の障害者台帳で確かめる必要がある（打合せ記録 U-3、照会 S-4）</t>
+          <t>論点メモが読んでいる版と正本が違う。正本の数値に読み替える。ただし正本の181人も他メンバーの策定ワークシートで「推計」と記された値であり、村の障害者台帳で確かめる必要がある（打合せ記録 U-3、照会 Ｓ-4）</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>目標は令和11年度末に置き直されている。「退院したい、家族と住みたいという意向」は目標の根拠として有用。移植の申し送り２（退院者1人の受け止め方）に本人の意向として加える。意向の確認時期と確認方法を村に確かめる（照会 M-27）</t>
+          <t>目標は令和11年度末に置き直されている。「退院したい、家族と住みたいという意向」は目標の根拠として有用。移植の申し送り２（退院者1人の受け止め方）に本人の意向として加える。意向の確認時期と確認方法を村に確かめる（照会 Ｍ-27）</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>一致しているため修正は要らない。高等部1名は令和9〜11年度に卒業する可能性があるため、卒業後の進路と必要なサービスを確かめる（照会 M-21）。「裏梯」は「裏磐梯」の誤記と読んだ</t>
+          <t>一致しているため修正は要らない。高等部1名は令和9〜11年度に卒業する可能性があるため、卒業後の進路と必要なサービスを確かめる（照会 Ｍ-21）。「裏梯」は「裏磐梯」の誤記と読んだ</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>障害者就業・生活支援センターを関係機関として明記する（別表第二 五㈠の記載事項）。物品調達の実績を村に確かめ、第３章５の進捗に入れる（照会 M-34）</t>
+          <t>障害者就業・生活支援センターを関係機関として明記する（別表第二 五㈠の記載事項）。物品調達の実績を村に確かめ、第３章５の進捗に入れる（照会 Ｍ-34）</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>移植の申し送り９に、社会福祉法改正（第2種事業）と権利擁護の窓口の検討を書き足す。村が検討しているかを確かめる（照会 M-35）</t>
+          <t>移植の申し送り９に、社会福祉法改正（第2種事業）と権利擁護の窓口の検討を書き足す。村が検討しているかを確かめる（照会 Ｍ-35）</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>個別避難計画を10件作るための手順として、名簿の更新・民生児童委員との連携・訓練の実施を書く。DIG・HUGは防災担当部局の所管であるため、実施状況を確かめたうえで連携として書く（照会 M-36）。移植の申し送り７（災害時にサービスを止めないための備え）とは別の論点（避難そのものへの備え）である点に注意</t>
+          <t>個別避難計画を10件作るための手順として、名簿の更新・民生児童委員との連携・訓練の実施を書く。DIG・HUGは防災担当部局の所管であるため、実施状況を確かめたうえで連携として書く（照会 Ｍ-36）。移植の申し送り７（災害時にサービスを止めないための備え）とは別の論点（避難そのものへの備え）である点に注意</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>共同生活援助（グループホーム。障害者総合支援法の訓練等給付）と福祉ホーム（地域生活支援事業の任意事業）は別の制度であり、どちらを設置するかで根拠も財源も変わる。村内に設置する予定があるのであれば、第５章２の確保方策と第５章１（３）の見込量に反映する必要がある。条例改正の要否も含めて村に確かめる（照会 M-37）</t>
+          <t>共同生活援助（グループホーム。障害者総合支援法の訓練等給付）と福祉ホーム（地域生活支援事業の任意事業）は別の制度であり、どちらを設置するかで根拠も財源も変わる。村内に設置する予定があるのであれば、第５章２の確保方策と第５章１（３）の見込量に反映する必要がある。条例改正の要否も含めて村に確かめる（照会 Ｍ-37）</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>当方の整理では40→68→69→72件と増加傾向としていた。減少の見通しがあるのであれば根拠が変わる。給付件数の大半を占める事業であり、事業費にも響くため、直近の増減の理由を村に確かめる（照会 M-38）</t>
+          <t>当方の整理では40→68→69→72件と増加傾向としていた。減少の見通しがあるのであれば根拠が変わる。給付件数の大半を占める事業であり、事業費にも響くため、直近の増減の理由を村に確かめる（照会 Ｍ-38）</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>42名と後見4・保佐2・補助1（計7名）が合わない。42は第６章の表にある精神障がい者30人＋知的障がい者12人＝42人と一致するため、取り違えの可能性がある。類型別の内訳は制度の見直し（後見・保佐を補助に一元化）との関係で重要なため、数値を確かめる（照会 M-39）</t>
+          <t>42名と後見4・保佐2・補助1（計7名）が合わない。42は第６章の表にある精神障がい者30人＋知的障がい者12人＝42人と一致するため、取り違えの可能性がある。類型別の内訳は制度の見直し（後見・保佐を補助に一元化）との関係で重要なため、数値を確かめる（照会 Ｍ-39）</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -2595,7 +2595,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>既存の村照会M-1〜M-33、県照会Q-1〜Q-8・S-11〜S-13、他メンバーへの確認S-1〜S-10・S-14〜S-18に続けて番号を付しました。</t>
+          <t>既存の村照会Ｍ-1〜Ｍ-33、県照会Q-1〜Q-8・Ｓ-11〜Ｓ-13、他メンバーへの確認Ｓ-1〜Ｓ-10・Ｓ-14〜Ｓ-18に続けて番号を付しました。</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>M-34</t>
+          <t>Ｍ-34</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -2666,7 +2666,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>M-35</t>
+          <t>Ｍ-35</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>M-36</t>
+          <t>Ｍ-36</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -2730,7 +2730,7 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>M-37</t>
+          <t>Ｍ-37</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -2762,7 +2762,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>M-38</t>
+          <t>Ｍ-38</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -2794,7 +2794,7 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>M-39</t>
+          <t>Ｍ-39</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
